--- a/erp-server/erp-server-fms/src/main/resources/excel/assetLocationTemplate.xlsx
+++ b/erp-server/erp-server-fms/src/main/resources/excel/assetLocationTemplate.xlsx
@@ -55,6 +55,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1236,9 +1243,7 @@
   <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.725" customWidth="1"/>
-    <col min="2" max="2" width="20.0916666666667" customWidth="1"/>
-    <col min="3" max="3" width="17.8166666666667" customWidth="1"/>
-    <col min="4" max="4" width="20.0916666666667" customWidth="1"/>
+    <col min="2" max="4" width="20.0916666666667" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="17.8166666666667" customWidth="1"/>
@@ -1267,15 +1272,11 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
-      <formula1>"办公领用,拍摄,研发,抖音直播,客服领用（客户指导使用）,参展,营销样品,认证检测,供应链生产组装,用户新品体验（仓库提供）,不良品分析（从售后仓领样）,星河线下领用,其他"</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
       <formula1>"公司内部使用,公司外部使用"</formula1>
     </dataValidation>
